--- a/data/EN/games_config/obscene_games_5_USA.xlsx
+++ b/data/EN/games_config/obscene_games_5_USA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\!Master\Tesis\3 Codigo\Cards_Against_AI\data\EN\games_config\games\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vfionda/Library/CloudStorage/GoogleDrive-valeria.fionda@unical.it/My Drive/didattica/Tesi/2025/Artigas Herold/Cards_Against_AI/data/EN/games_config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726D533C-90C5-46C6-8EB7-93C6816E38ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E34E73-ED85-BA42-A384-EDD464BD03BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28520" windowHeight="28960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="455">
   <si>
     <t>black_id</t>
   </si>
@@ -1353,9 +1353,6 @@
   </si>
   <si>
     <t>W204</t>
-  </si>
-  <si>
-    <t>w213</t>
   </si>
   <si>
     <t>W123</t>
@@ -1419,6 +1416,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1764,19 +1762,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J174"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="9" width="11.1640625" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>93</v>
       </c>
@@ -1802,7 +1799,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -1825,7 +1822,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -1848,7 +1845,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -1871,7 +1868,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -1894,7 +1891,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -1917,7 +1914,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -1940,7 +1937,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>94</v>
       </c>
@@ -1963,7 +1960,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -1986,7 +1983,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -2009,7 +2006,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>94</v>
       </c>
@@ -2032,7 +2029,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -2055,7 +2052,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -2078,7 +2075,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -2101,7 +2098,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -2124,7 +2121,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -2147,7 +2144,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -2170,7 +2167,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -2193,7 +2190,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -2216,7 +2213,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -2239,7 +2236,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -2262,7 +2259,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -2285,7 +2282,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -2308,7 +2305,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>94</v>
       </c>
@@ -2331,7 +2328,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>94</v>
       </c>
@@ -2354,7 +2351,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -2377,7 +2374,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>94</v>
       </c>
@@ -2400,7 +2397,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -2423,7 +2420,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>94</v>
       </c>
@@ -2446,7 +2443,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>94</v>
       </c>
@@ -2469,7 +2466,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -2492,7 +2489,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -2515,7 +2512,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -2538,7 +2535,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>94</v>
       </c>
@@ -2561,7 +2558,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -2584,7 +2581,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>94</v>
       </c>
@@ -2607,7 +2604,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>94</v>
       </c>
@@ -2630,7 +2627,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>94</v>
       </c>
@@ -2653,7 +2650,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -2676,7 +2673,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -2699,7 +2696,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>94</v>
       </c>
@@ -2722,7 +2719,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2745,7 +2742,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -2768,7 +2765,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2791,7 +2788,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>94</v>
       </c>
@@ -2814,7 +2811,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -2837,7 +2834,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>94</v>
       </c>
@@ -2860,7 +2857,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -2883,7 +2880,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -2906,7 +2903,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -2929,7 +2926,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>94</v>
       </c>
@@ -2952,7 +2949,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>94</v>
       </c>
@@ -2975,7 +2972,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>94</v>
       </c>
@@ -2998,7 +2995,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>94</v>
       </c>
@@ -3021,7 +3018,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -3044,7 +3041,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>94</v>
       </c>
@@ -3067,7 +3064,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>94</v>
       </c>
@@ -3090,7 +3087,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>94</v>
       </c>
@@ -3113,7 +3110,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -3136,7 +3133,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>94</v>
       </c>
@@ -3159,7 +3156,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>94</v>
       </c>
@@ -3182,7 +3179,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>94</v>
       </c>
@@ -3205,7 +3202,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>94</v>
       </c>
@@ -3228,7 +3225,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>94</v>
       </c>
@@ -3251,7 +3248,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -3274,7 +3271,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -3297,7 +3294,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>94</v>
       </c>
@@ -3320,7 +3317,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>94</v>
       </c>
@@ -3334,7 +3331,7 @@
         <v>265</v>
       </c>
       <c r="E68" t="s">
-        <v>440</v>
+        <v>401</v>
       </c>
       <c r="F68" t="s">
         <v>377</v>
@@ -3343,7 +3340,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>94</v>
       </c>
@@ -3366,7 +3363,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>94</v>
       </c>
@@ -3389,7 +3386,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>94</v>
       </c>
@@ -3406,13 +3403,13 @@
         <v>355</v>
       </c>
       <c r="F71" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G71" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>94</v>
       </c>
@@ -3426,7 +3423,7 @@
         <v>427</v>
       </c>
       <c r="E72" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F72" t="s">
         <v>400</v>
@@ -3435,7 +3432,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>94</v>
       </c>
@@ -3458,7 +3455,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>94</v>
       </c>
@@ -3481,7 +3478,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>94</v>
       </c>
@@ -3504,7 +3501,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>94</v>
       </c>
@@ -3518,7 +3515,7 @@
         <v>302</v>
       </c>
       <c r="E76" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F76" t="s">
         <v>390</v>
@@ -3527,7 +3524,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>94</v>
       </c>
@@ -3550,7 +3547,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>94</v>
       </c>
@@ -3573,7 +3570,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>94</v>
       </c>
@@ -3596,7 +3593,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -3619,7 +3616,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>94</v>
       </c>
@@ -3633,7 +3630,7 @@
         <v>272</v>
       </c>
       <c r="E81" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F81" t="s">
         <v>379</v>
@@ -3642,7 +3639,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>94</v>
       </c>
@@ -3665,7 +3662,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -3679,7 +3676,7 @@
         <v>261</v>
       </c>
       <c r="E83" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F83" t="s">
         <v>402</v>
@@ -3688,7 +3685,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -3711,7 +3708,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -3734,7 +3731,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>94</v>
       </c>
@@ -3757,7 +3754,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>94</v>
       </c>
@@ -3771,7 +3768,7 @@
         <v>276</v>
       </c>
       <c r="E87" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F87" t="s">
         <v>376</v>
@@ -3780,7 +3777,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>94</v>
       </c>
@@ -3797,13 +3794,13 @@
         <v>340</v>
       </c>
       <c r="F88" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G88" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>94</v>
       </c>
@@ -3826,7 +3823,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -3849,7 +3846,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -3866,13 +3863,13 @@
         <v>321</v>
       </c>
       <c r="F91" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G91" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -3895,7 +3892,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -3918,7 +3915,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -3941,7 +3938,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -3964,7 +3961,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -3987,7 +3984,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>94</v>
       </c>
@@ -4010,7 +4007,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>94</v>
       </c>
@@ -4033,7 +4030,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>94</v>
       </c>
@@ -4047,7 +4044,7 @@
         <v>281</v>
       </c>
       <c r="E99" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F99" t="s">
         <v>390</v>
@@ -4056,7 +4053,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>94</v>
       </c>
@@ -4079,7 +4076,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>94</v>
       </c>
@@ -4102,7 +4099,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>94</v>
       </c>
@@ -4125,7 +4122,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>94</v>
       </c>
@@ -4148,7 +4145,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>94</v>
       </c>
@@ -4171,7 +4168,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>94</v>
       </c>
@@ -4185,7 +4182,7 @@
         <v>261</v>
       </c>
       <c r="E105" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F105" t="s">
         <v>329</v>
@@ -4194,7 +4191,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>94</v>
       </c>
@@ -4217,7 +4214,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>94</v>
       </c>
@@ -4240,7 +4237,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -4254,7 +4251,7 @@
         <v>265</v>
       </c>
       <c r="E108" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F108" t="s">
         <v>413</v>
@@ -4263,7 +4260,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>94</v>
       </c>
@@ -4286,7 +4283,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>94</v>
       </c>
@@ -4309,7 +4306,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>94</v>
       </c>
@@ -4332,7 +4329,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>94</v>
       </c>
@@ -4355,7 +4352,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>94</v>
       </c>
@@ -4378,7 +4375,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>94</v>
       </c>
@@ -4401,7 +4398,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>94</v>
       </c>
@@ -4424,7 +4421,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>94</v>
       </c>
@@ -4447,7 +4444,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>94</v>
       </c>
@@ -4470,7 +4467,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>94</v>
       </c>
@@ -4493,7 +4490,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>94</v>
       </c>
@@ -4516,7 +4513,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>94</v>
       </c>
@@ -4530,7 +4527,7 @@
         <v>318</v>
       </c>
       <c r="E120" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F120" t="s">
         <v>378</v>
@@ -4539,7 +4536,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>94</v>
       </c>
@@ -4562,7 +4559,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>94</v>
       </c>
@@ -4585,7 +4582,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>94</v>
       </c>
@@ -4599,7 +4596,7 @@
         <v>182</v>
       </c>
       <c r="E123" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F123" t="s">
         <v>390</v>
@@ -4608,7 +4605,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>94</v>
       </c>
@@ -4631,7 +4628,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>94</v>
       </c>
@@ -4654,7 +4651,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>94</v>
       </c>
@@ -4677,7 +4674,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>94</v>
       </c>
@@ -4700,7 +4697,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>94</v>
       </c>
@@ -4714,7 +4711,7 @@
         <v>281</v>
       </c>
       <c r="E128" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F128" t="s">
         <v>361</v>
@@ -4723,7 +4720,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>94</v>
       </c>
@@ -4746,7 +4743,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>94</v>
       </c>
@@ -4769,7 +4766,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>94</v>
       </c>
@@ -4792,7 +4789,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>94</v>
       </c>
@@ -4815,7 +4812,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>94</v>
       </c>
@@ -4838,7 +4835,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>94</v>
       </c>
@@ -4861,7 +4858,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>94</v>
       </c>
@@ -4878,13 +4875,13 @@
         <v>360</v>
       </c>
       <c r="F135" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G135" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>94</v>
       </c>
@@ -4907,7 +4904,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>94</v>
       </c>
@@ -4921,7 +4918,7 @@
         <v>264</v>
       </c>
       <c r="E137" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F137" t="s">
         <v>420</v>
@@ -4930,7 +4927,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>94</v>
       </c>
@@ -4953,7 +4950,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>94</v>
       </c>
@@ -4976,7 +4973,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>94</v>
       </c>
@@ -4993,13 +4990,13 @@
         <v>344</v>
       </c>
       <c r="F140" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G140" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>94</v>
       </c>
@@ -5022,7 +5019,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>94</v>
       </c>
@@ -5045,7 +5042,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>94</v>
       </c>
@@ -5068,7 +5065,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>94</v>
       </c>
@@ -5091,7 +5088,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>94</v>
       </c>
@@ -5114,7 +5111,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>94</v>
       </c>
@@ -5128,7 +5125,7 @@
         <v>264</v>
       </c>
       <c r="E146" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F146" t="s">
         <v>396</v>
@@ -5137,7 +5134,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>94</v>
       </c>
@@ -5160,7 +5157,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>94</v>
       </c>
@@ -5183,7 +5180,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>94</v>
       </c>
@@ -5200,13 +5197,13 @@
         <v>325</v>
       </c>
       <c r="F149" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G149" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>94</v>
       </c>
@@ -5229,7 +5226,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>94</v>
       </c>
@@ -5252,7 +5249,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>94</v>
       </c>
@@ -5275,7 +5272,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>94</v>
       </c>
@@ -5298,7 +5295,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>94</v>
       </c>
@@ -5321,7 +5318,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>94</v>
       </c>
@@ -5344,7 +5341,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>94</v>
       </c>
@@ -5367,7 +5364,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>94</v>
       </c>
@@ -5390,7 +5387,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>94</v>
       </c>
@@ -5413,7 +5410,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>94</v>
       </c>
@@ -5436,7 +5433,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>94</v>
       </c>
@@ -5459,7 +5456,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>94</v>
       </c>
@@ -5482,7 +5479,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>94</v>
       </c>
@@ -5505,7 +5502,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>94</v>
       </c>
@@ -5528,7 +5525,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>94</v>
       </c>
@@ -5551,7 +5548,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>94</v>
       </c>
@@ -5574,7 +5571,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>94</v>
       </c>
@@ -5597,7 +5594,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>94</v>
       </c>
@@ -5611,7 +5608,7 @@
         <v>280</v>
       </c>
       <c r="E167" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F167" t="s">
         <v>377</v>
@@ -5620,7 +5617,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>94</v>
       </c>
@@ -5643,7 +5640,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>94</v>
       </c>
@@ -5666,7 +5663,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>94</v>
       </c>
@@ -5689,7 +5686,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>94</v>
       </c>
@@ -5706,13 +5703,13 @@
         <v>390</v>
       </c>
       <c r="F171" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G171" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>94</v>
       </c>
@@ -5735,7 +5732,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>94</v>
       </c>
@@ -5758,7 +5755,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>94</v>
       </c>

--- a/data/EN/games_config/obscene_games_5_USA.xlsx
+++ b/data/EN/games_config/obscene_games_5_USA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vfionda/Library/CloudStorage/GoogleDrive-valeria.fionda@unical.it/My Drive/didattica/Tesi/2025/Artigas Herold/Cards_Against_AI/data/EN/games_config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\!Master\Tesis\3 Codigo\Cards_Against_AI\data\EN\games_config\games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E34E73-ED85-BA42-A384-EDD464BD03BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726D533C-90C5-46C6-8EB7-93C6816E38ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28520" windowHeight="28960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="456">
   <si>
     <t>black_id</t>
   </si>
@@ -1353,6 +1353,9 @@
   </si>
   <si>
     <t>W204</t>
+  </si>
+  <si>
+    <t>w213</t>
   </si>
   <si>
     <t>W123</t>
@@ -1416,7 +1419,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1762,18 +1764,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J174"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="9" width="11.1640625" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>93</v>
       </c>
@@ -1799,7 +1802,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>94</v>
       </c>
@@ -1822,7 +1825,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -1845,7 +1848,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -1868,7 +1871,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -1891,7 +1894,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -1914,7 +1917,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -1937,7 +1940,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>94</v>
       </c>
@@ -1960,7 +1963,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -1983,7 +1986,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -2006,7 +2009,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>94</v>
       </c>
@@ -2029,7 +2032,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -2052,7 +2055,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -2075,7 +2078,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -2098,7 +2101,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -2121,7 +2124,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -2144,7 +2147,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -2167,7 +2170,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -2190,7 +2193,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>94</v>
       </c>
@@ -2213,7 +2216,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>94</v>
       </c>
@@ -2236,7 +2239,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -2259,7 +2262,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -2282,7 +2285,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -2305,7 +2308,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>94</v>
       </c>
@@ -2328,7 +2331,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>94</v>
       </c>
@@ -2351,7 +2354,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -2374,7 +2377,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>94</v>
       </c>
@@ -2397,7 +2400,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -2420,7 +2423,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>94</v>
       </c>
@@ -2443,7 +2446,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>94</v>
       </c>
@@ -2466,7 +2469,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>94</v>
       </c>
@@ -2489,7 +2492,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -2512,7 +2515,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>94</v>
       </c>
@@ -2535,7 +2538,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>94</v>
       </c>
@@ -2558,7 +2561,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>94</v>
       </c>
@@ -2581,7 +2584,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>94</v>
       </c>
@@ -2604,7 +2607,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>94</v>
       </c>
@@ -2627,7 +2630,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>94</v>
       </c>
@@ -2650,7 +2653,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -2673,7 +2676,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -2696,7 +2699,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>94</v>
       </c>
@@ -2719,7 +2722,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -2742,7 +2745,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -2765,7 +2768,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2788,7 +2791,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>94</v>
       </c>
@@ -2811,7 +2814,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>94</v>
       </c>
@@ -2834,7 +2837,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>94</v>
       </c>
@@ -2857,7 +2860,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -2880,7 +2883,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -2903,7 +2906,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -2926,7 +2929,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>94</v>
       </c>
@@ -2949,7 +2952,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>94</v>
       </c>
@@ -2972,7 +2975,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>94</v>
       </c>
@@ -2995,7 +2998,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>94</v>
       </c>
@@ -3018,7 +3021,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -3041,7 +3044,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>94</v>
       </c>
@@ -3064,7 +3067,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>94</v>
       </c>
@@ -3087,7 +3090,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>94</v>
       </c>
@@ -3110,7 +3113,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -3133,7 +3136,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>94</v>
       </c>
@@ -3156,7 +3159,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>94</v>
       </c>
@@ -3179,7 +3182,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>94</v>
       </c>
@@ -3202,7 +3205,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>94</v>
       </c>
@@ -3225,7 +3228,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>94</v>
       </c>
@@ -3248,7 +3251,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -3271,7 +3274,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -3294,7 +3297,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>94</v>
       </c>
@@ -3317,7 +3320,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>94</v>
       </c>
@@ -3331,7 +3334,7 @@
         <v>265</v>
       </c>
       <c r="E68" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="F68" t="s">
         <v>377</v>
@@ -3340,7 +3343,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>94</v>
       </c>
@@ -3363,7 +3366,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>94</v>
       </c>
@@ -3386,7 +3389,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>94</v>
       </c>
@@ -3403,13 +3406,13 @@
         <v>355</v>
       </c>
       <c r="F71" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G71" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>94</v>
       </c>
@@ -3423,7 +3426,7 @@
         <v>427</v>
       </c>
       <c r="E72" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F72" t="s">
         <v>400</v>
@@ -3432,7 +3435,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>94</v>
       </c>
@@ -3455,7 +3458,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>94</v>
       </c>
@@ -3478,7 +3481,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>94</v>
       </c>
@@ -3501,7 +3504,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>94</v>
       </c>
@@ -3515,7 +3518,7 @@
         <v>302</v>
       </c>
       <c r="E76" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F76" t="s">
         <v>390</v>
@@ -3524,7 +3527,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>94</v>
       </c>
@@ -3547,7 +3550,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>94</v>
       </c>
@@ -3570,7 +3573,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>94</v>
       </c>
@@ -3593,7 +3596,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -3616,7 +3619,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>94</v>
       </c>
@@ -3630,7 +3633,7 @@
         <v>272</v>
       </c>
       <c r="E81" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F81" t="s">
         <v>379</v>
@@ -3639,7 +3642,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>94</v>
       </c>
@@ -3662,7 +3665,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -3676,7 +3679,7 @@
         <v>261</v>
       </c>
       <c r="E83" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F83" t="s">
         <v>402</v>
@@ -3685,7 +3688,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -3708,7 +3711,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>94</v>
       </c>
@@ -3731,7 +3734,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>94</v>
       </c>
@@ -3754,7 +3757,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>94</v>
       </c>
@@ -3768,7 +3771,7 @@
         <v>276</v>
       </c>
       <c r="E87" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F87" t="s">
         <v>376</v>
@@ -3777,7 +3780,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>94</v>
       </c>
@@ -3794,13 +3797,13 @@
         <v>340</v>
       </c>
       <c r="F88" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G88" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>94</v>
       </c>
@@ -3823,7 +3826,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -3846,7 +3849,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -3863,13 +3866,13 @@
         <v>321</v>
       </c>
       <c r="F91" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G91" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -3892,7 +3895,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -3915,7 +3918,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -3938,7 +3941,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -3961,7 +3964,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -3984,7 +3987,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>94</v>
       </c>
@@ -4007,7 +4010,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>94</v>
       </c>
@@ -4030,7 +4033,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>94</v>
       </c>
@@ -4044,7 +4047,7 @@
         <v>281</v>
       </c>
       <c r="E99" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F99" t="s">
         <v>390</v>
@@ -4053,7 +4056,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>94</v>
       </c>
@@ -4076,7 +4079,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>94</v>
       </c>
@@ -4099,7 +4102,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>94</v>
       </c>
@@ -4122,7 +4125,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>94</v>
       </c>
@@ -4145,7 +4148,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>94</v>
       </c>
@@ -4168,7 +4171,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>94</v>
       </c>
@@ -4182,7 +4185,7 @@
         <v>261</v>
       </c>
       <c r="E105" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F105" t="s">
         <v>329</v>
@@ -4191,7 +4194,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>94</v>
       </c>
@@ -4214,7 +4217,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>94</v>
       </c>
@@ -4237,7 +4240,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -4251,7 +4254,7 @@
         <v>265</v>
       </c>
       <c r="E108" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F108" t="s">
         <v>413</v>
@@ -4260,7 +4263,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>94</v>
       </c>
@@ -4283,7 +4286,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>94</v>
       </c>
@@ -4306,7 +4309,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>94</v>
       </c>
@@ -4329,7 +4332,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>94</v>
       </c>
@@ -4352,7 +4355,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>94</v>
       </c>
@@ -4375,7 +4378,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>94</v>
       </c>
@@ -4398,7 +4401,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>94</v>
       </c>
@@ -4421,7 +4424,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>94</v>
       </c>
@@ -4444,7 +4447,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>94</v>
       </c>
@@ -4467,7 +4470,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>94</v>
       </c>
@@ -4490,7 +4493,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>94</v>
       </c>
@@ -4513,7 +4516,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>94</v>
       </c>
@@ -4527,7 +4530,7 @@
         <v>318</v>
       </c>
       <c r="E120" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F120" t="s">
         <v>378</v>
@@ -4536,7 +4539,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>94</v>
       </c>
@@ -4559,7 +4562,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>94</v>
       </c>
@@ -4582,7 +4585,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>94</v>
       </c>
@@ -4596,7 +4599,7 @@
         <v>182</v>
       </c>
       <c r="E123" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F123" t="s">
         <v>390</v>
@@ -4605,7 +4608,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>94</v>
       </c>
@@ -4628,7 +4631,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>94</v>
       </c>
@@ -4651,7 +4654,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>94</v>
       </c>
@@ -4674,7 +4677,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>94</v>
       </c>
@@ -4697,7 +4700,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>94</v>
       </c>
@@ -4711,7 +4714,7 @@
         <v>281</v>
       </c>
       <c r="E128" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F128" t="s">
         <v>361</v>
@@ -4720,7 +4723,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>94</v>
       </c>
@@ -4743,7 +4746,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>94</v>
       </c>
@@ -4766,7 +4769,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>94</v>
       </c>
@@ -4789,7 +4792,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>94</v>
       </c>
@@ -4812,7 +4815,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>94</v>
       </c>
@@ -4835,7 +4838,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>94</v>
       </c>
@@ -4858,7 +4861,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>94</v>
       </c>
@@ -4875,13 +4878,13 @@
         <v>360</v>
       </c>
       <c r="F135" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G135" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>94</v>
       </c>
@@ -4904,7 +4907,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>94</v>
       </c>
@@ -4918,7 +4921,7 @@
         <v>264</v>
       </c>
       <c r="E137" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F137" t="s">
         <v>420</v>
@@ -4927,7 +4930,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>94</v>
       </c>
@@ -4950,7 +4953,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>94</v>
       </c>
@@ -4973,7 +4976,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>94</v>
       </c>
@@ -4990,13 +4993,13 @@
         <v>344</v>
       </c>
       <c r="F140" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G140" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>94</v>
       </c>
@@ -5019,7 +5022,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>94</v>
       </c>
@@ -5042,7 +5045,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>94</v>
       </c>
@@ -5065,7 +5068,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>94</v>
       </c>
@@ -5088,7 +5091,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>94</v>
       </c>
@@ -5111,7 +5114,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>94</v>
       </c>
@@ -5125,7 +5128,7 @@
         <v>264</v>
       </c>
       <c r="E146" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F146" t="s">
         <v>396</v>
@@ -5134,7 +5137,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>94</v>
       </c>
@@ -5157,7 +5160,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>94</v>
       </c>
@@ -5180,7 +5183,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>94</v>
       </c>
@@ -5197,13 +5200,13 @@
         <v>325</v>
       </c>
       <c r="F149" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G149" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>94</v>
       </c>
@@ -5226,7 +5229,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>94</v>
       </c>
@@ -5249,7 +5252,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>94</v>
       </c>
@@ -5272,7 +5275,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>94</v>
       </c>
@@ -5295,7 +5298,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>94</v>
       </c>
@@ -5318,7 +5321,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>94</v>
       </c>
@@ -5341,7 +5344,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>94</v>
       </c>
@@ -5364,7 +5367,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>94</v>
       </c>
@@ -5387,7 +5390,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>94</v>
       </c>
@@ -5410,7 +5413,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>94</v>
       </c>
@@ -5433,7 +5436,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>94</v>
       </c>
@@ -5456,7 +5459,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>94</v>
       </c>
@@ -5479,7 +5482,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>94</v>
       </c>
@@ -5502,7 +5505,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>94</v>
       </c>
@@ -5525,7 +5528,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>94</v>
       </c>
@@ -5548,7 +5551,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>94</v>
       </c>
@@ -5571,7 +5574,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>94</v>
       </c>
@@ -5594,7 +5597,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>94</v>
       </c>
@@ -5608,7 +5611,7 @@
         <v>280</v>
       </c>
       <c r="E167" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F167" t="s">
         <v>377</v>
@@ -5617,7 +5620,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>94</v>
       </c>
@@ -5640,7 +5643,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>94</v>
       </c>
@@ -5663,7 +5666,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>94</v>
       </c>
@@ -5686,7 +5689,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>94</v>
       </c>
@@ -5703,13 +5706,13 @@
         <v>390</v>
       </c>
       <c r="F171" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G171" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>94</v>
       </c>
@@ -5732,7 +5735,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>94</v>
       </c>
@@ -5755,7 +5758,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>94</v>
       </c>
